--- a/data/trans_camb/IP08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 4,71</t>
+          <t>-7,99; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 3,63</t>
+          <t>-8,93; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,06</t>
+          <t>-5,81; 7,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 3,41</t>
+          <t>-10,53; 2,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 2,5</t>
+          <t>-10,55; 2,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 5,27</t>
+          <t>-8,46; 5,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 2,04</t>
+          <t>-7,04; 2,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 1,53</t>
+          <t>-7,96; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 4,29</t>
+          <t>-5,39; 4,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,94; 80,88</t>
+          <t>-68,14; 80,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 64,88</t>
+          <t>-73,75; 84,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 118,31</t>
+          <t>-44,76; 124,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 44,8</t>
+          <t>-67,15; 46,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 35,99</t>
+          <t>-68,78; 36,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 72,91</t>
+          <t>-55,77; 61,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 26,94</t>
+          <t>-55,8; 27,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 21,6</t>
+          <t>-59,48; 24,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 54,3</t>
+          <t>-41,51; 54,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 7,11</t>
+          <t>-6,22; 7,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -1,16</t>
+          <t>-12,91; -1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 6,78</t>
+          <t>-7,08; 6,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 4,98</t>
+          <t>-8,48; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 3,87</t>
+          <t>-9,86; 3,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 9,74</t>
+          <t>-5,94; 10,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 4,23</t>
+          <t>-6,33; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -0,51</t>
+          <t>-9,04; -0,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 6,06</t>
+          <t>-4,71; 5,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 147,91</t>
+          <t>-53,19; 138,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-93,95; -9,59</t>
+          <t>-94,65; -3,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 122,84</t>
+          <t>-60,17; 136,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 75,47</t>
+          <t>-59,82; 89,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,1; 67,93</t>
+          <t>-66,56; 58,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 139,01</t>
+          <t>-46,5; 148,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 63,37</t>
+          <t>-50,36; 62,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,49; -5,23</t>
+          <t>-73,82; -5,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 84,3</t>
+          <t>-40,43; 84,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 10,24</t>
+          <t>-2,74; 10,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,93</t>
+          <t>-6,43; 5,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 6,7</t>
+          <t>-6,83; 7,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 8,62</t>
+          <t>-8,16; 7,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 1,28</t>
+          <t>-13,87; 1,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 7,59</t>
+          <t>-10,53; 8,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,65</t>
+          <t>-4,75; 6,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 1,59</t>
+          <t>-9,08; 1,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 5,28</t>
+          <t>-7,35; 4,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 389,76</t>
+          <t>-35,64; 453,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,04; 237,9</t>
+          <t>-79,06; 210,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,42; 334,89</t>
+          <t>-81,84; 286,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 84,83</t>
+          <t>-46,18; 77,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 13,0</t>
+          <t>-78,25; 21,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,09; 84,49</t>
+          <t>-61,32; 88,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 85,98</t>
+          <t>-36,0; 81,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,13; 22,35</t>
+          <t>-68,25; 18,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 66,62</t>
+          <t>-56,62; 47,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 13,66</t>
+          <t>2,67; 13,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 2,95</t>
+          <t>-5,2; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 11,86</t>
+          <t>-2,97; 12,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 12,84</t>
+          <t>1,99; 12,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,77</t>
+          <t>-9,77; -0,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 10,16</t>
+          <t>-0,6; 10,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 11,8</t>
+          <t>3,97; 11,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,46</t>
+          <t>-5,77; 0,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 8,71</t>
+          <t>-0,5; 8,07</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,24; 208,36</t>
+          <t>22,59; 205,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 48,61</t>
+          <t>-47,81; 58,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 164,16</t>
+          <t>-28,81; 157,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,1; 162,77</t>
+          <t>14,8; 162,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,26; -6,83</t>
+          <t>-73,26; -5,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 133,41</t>
+          <t>-4,96; 136,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,78; 154,6</t>
+          <t>33,88; 149,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 6,58</t>
+          <t>-52,79; 5,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 113,48</t>
+          <t>-5,88; 99,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 9,83</t>
+          <t>-3,16; 9,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 7,85</t>
+          <t>-4,58; 7,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 9,2</t>
+          <t>-4,18; 9,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,56</t>
+          <t>-2,83; 11,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 0,23</t>
+          <t>-11,79; 0,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 22,79</t>
+          <t>-5,62; 21,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 8,15</t>
+          <t>-1,21; 7,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 1,72</t>
+          <t>-6,66; 2,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 15,16</t>
+          <t>-2,43; 16,52</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 186,52</t>
+          <t>-28,98; 174,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 168,7</t>
+          <t>-42,32; 157,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 178,15</t>
+          <t>-35,54; 189,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 114,59</t>
+          <t>-18,35; 122,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 5,04</t>
+          <t>-74,87; 7,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 248,62</t>
+          <t>-41,36; 205,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 94,92</t>
+          <t>-9,82; 91,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 21,66</t>
+          <t>-49,26; 26,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 170,18</t>
+          <t>-21,53; 177,73</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,79</t>
+          <t>-5,58; 10,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 4,75</t>
+          <t>-8,6; 5,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,68</t>
+          <t>-8,32; 5,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 5,67</t>
+          <t>-9,26; 6,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 8,11</t>
+          <t>-8,71; 8,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 5,15</t>
+          <t>-11,29; 4,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,23</t>
+          <t>-4,67; 6,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,24</t>
+          <t>-6,65; 4,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,63</t>
+          <t>-6,69; 3,52</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-62,25; 255,43</t>
+          <t>-60,16; 337,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-87,01; 145,4</t>
+          <t>-86,09; 175,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 186,57</t>
+          <t>-76,98; 217,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 90,39</t>
+          <t>-62,36; 91,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 113,41</t>
+          <t>-59,65; 144,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 81,95</t>
+          <t>-73,75; 71,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 107,13</t>
+          <t>-43,67; 110,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 90,98</t>
+          <t>-58,27; 76,77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 63,88</t>
+          <t>-57,85; 54,38</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,37</t>
+          <t>0,82; 6,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,74</t>
+          <t>-3,83; 0,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,73</t>
+          <t>-1,16; 4,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,28</t>
+          <t>-0,59; 4,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -2,0</t>
+          <t>-6,79; -1,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 6,12</t>
+          <t>-1,71; 5,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,77</t>
+          <t>0,88; 4,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -1,34</t>
+          <t>-4,92; -1,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,39</t>
+          <t>-0,79; 4,35</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>11,03; 89,36</t>
+          <t>9,06; 90,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 10,69</t>
+          <t>-39,8; 10,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 66,75</t>
+          <t>-12,93; 68,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 53,89</t>
+          <t>-4,55; 49,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -20,09</t>
+          <t>-53,77; -17,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 59,68</t>
+          <t>-14,51; 54,91</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,92; 54,44</t>
+          <t>7,9; 53,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,17; -15,03</t>
+          <t>-45,14; -13,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 48,1</t>
+          <t>-7,56; 48,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 4,63</t>
+          <t>-7,84; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 4,17</t>
+          <t>-8,14; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,48</t>
+          <t>-6,45; 7,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 2,98</t>
+          <t>-10,59; 3,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 2,32</t>
+          <t>-11,15; 1,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 5,0</t>
+          <t>-8,65; 5,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,1</t>
+          <t>-6,88; 2,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 1,57</t>
+          <t>-7,87; 1,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,36</t>
+          <t>-5,02; 4,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 80,91</t>
+          <t>-66,2; 83,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 84,65</t>
+          <t>-68,61; 70,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 124,58</t>
+          <t>-48,73; 121,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,15; 46,12</t>
+          <t>-68,39; 42,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 36,83</t>
+          <t>-72,36; 24,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,77; 61,9</t>
+          <t>-55,49; 71,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 27,94</t>
+          <t>-56,48; 30,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,48; 24,47</t>
+          <t>-63,34; 14,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 54,09</t>
+          <t>-39,98; 59,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 7,37</t>
+          <t>-6,95; 7,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -1,03</t>
+          <t>-12,93; -1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 6,63</t>
+          <t>-6,68; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 5,37</t>
+          <t>-9,04; 4,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 3,52</t>
+          <t>-8,92; 3,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 10,23</t>
+          <t>-5,21; 10,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 4,1</t>
+          <t>-5,66; 4,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -0,55</t>
+          <t>-9,13; -0,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 5,83</t>
+          <t>-4,25; 6,39</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 138,77</t>
+          <t>-55,61; 151,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,65; -3,63</t>
+          <t>-94,3; 1,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 136,07</t>
+          <t>-54,43; 147,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 89,62</t>
+          <t>-62,71; 78,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 58,25</t>
+          <t>-64,04; 69,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 148,9</t>
+          <t>-43,48; 149,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 62,31</t>
+          <t>-46,88; 60,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,82; -5,98</t>
+          <t>-72,93; 0,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 84,05</t>
+          <t>-37,69; 98,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 10,98</t>
+          <t>-3,35; 10,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,9</t>
+          <t>-6,37; 6,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,1</t>
+          <t>-6,94; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 7,73</t>
+          <t>-7,77; 8,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 1,2</t>
+          <t>-12,86; 0,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 8,11</t>
+          <t>-10,52; 8,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,53</t>
+          <t>-4,44; 6,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,28</t>
+          <t>-8,97; 1,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,02</t>
+          <t>-6,96; 5,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 453,29</t>
+          <t>-45,56; 428,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,06; 210,0</t>
+          <t>-76,58; 322,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,84; 286,31</t>
+          <t>-81,59; 351,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,18; 77,87</t>
+          <t>-44,92; 91,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 21,0</t>
+          <t>-75,78; 12,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,32; 88,22</t>
+          <t>-64,05; 90,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 81,83</t>
+          <t>-33,27; 87,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 18,01</t>
+          <t>-66,41; 26,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 47,25</t>
+          <t>-56,73; 72,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 13,17</t>
+          <t>3,03; 13,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,55</t>
+          <t>-5,47; 3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 12,55</t>
+          <t>-2,91; 11,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 12,49</t>
+          <t>1,89; 12,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -0,56</t>
+          <t>-8,74; -0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 10,2</t>
+          <t>-0,73; 10,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,6</t>
+          <t>3,91; 11,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,32</t>
+          <t>-5,84; 0,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,07</t>
+          <t>-0,65; 8,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,59; 205,03</t>
+          <t>24,38; 199,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 58,5</t>
+          <t>-48,84; 50,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 157,14</t>
+          <t>-29,89; 179,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,8; 162,48</t>
+          <t>13,31; 171,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,26; -5,06</t>
+          <t>-71,92; -3,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 136,11</t>
+          <t>-8,86; 128,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,88; 149,14</t>
+          <t>35,94; 151,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 5,91</t>
+          <t>-53,03; 2,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 99,56</t>
+          <t>-7,53; 104,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 9,35</t>
+          <t>-3,14; 8,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 7,81</t>
+          <t>-4,41; 7,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 9,27</t>
+          <t>-3,29; 9,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 11,29</t>
+          <t>-3,0; 11,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 0,13</t>
+          <t>-12,36; -0,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 21,57</t>
+          <t>-5,35; 23,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 7,83</t>
+          <t>-1,35; 8,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 2,11</t>
+          <t>-6,72; 2,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 16,52</t>
+          <t>-2,39; 15,73</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 174,16</t>
+          <t>-28,77; 175,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 157,61</t>
+          <t>-40,7; 158,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 189,88</t>
+          <t>-34,0; 172,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 122,26</t>
+          <t>-19,11; 119,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,87; 7,53</t>
+          <t>-74,6; 0,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 205,03</t>
+          <t>-39,18; 234,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 91,74</t>
+          <t>-10,75; 102,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 26,02</t>
+          <t>-52,74; 25,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 177,73</t>
+          <t>-21,12; 174,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 10,61</t>
+          <t>-5,09; 10,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,19</t>
+          <t>-8,74; 4,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 5,91</t>
+          <t>-8,0; 5,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 6,02</t>
+          <t>-9,59; 6,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 8,88</t>
+          <t>-8,87; 8,35</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 4,57</t>
+          <t>-10,62; 4,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,42</t>
+          <t>-5,33; 6,01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 4,65</t>
+          <t>-6,88; 3,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 3,52</t>
+          <t>-7,24; 3,16</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 337,11</t>
+          <t>-61,13; 322,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-86,09; 175,2</t>
+          <t>-86,44; 132,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-76,98; 217,62</t>
+          <t>-77,71; 162,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 91,63</t>
+          <t>-64,08; 91,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-59,65; 144,1</t>
+          <t>-60,18; 130,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 71,81</t>
+          <t>-73,16; 71,43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 110,05</t>
+          <t>-49,14; 95,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 76,77</t>
+          <t>-59,23; 66,38</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 54,38</t>
+          <t>-65,48; 58,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,22</t>
+          <t>0,84; 6,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,76</t>
+          <t>-4,01; 0,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,77</t>
+          <t>-1,49; 4,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 4,97</t>
+          <t>-0,72; 5,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -1,79</t>
+          <t>-7,0; -1,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,76</t>
+          <t>-1,9; 6,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,78</t>
+          <t>0,71; 4,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -1,22</t>
+          <t>-4,74; -1,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,35</t>
+          <t>-0,69; 4,37</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,06; 90,09</t>
+          <t>8,03; 87,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 10,86</t>
+          <t>-41,65; 12,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 68,06</t>
+          <t>-16,39; 65,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 49,22</t>
+          <t>-5,07; 52,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -17,37</t>
+          <t>-53,25; -18,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 54,91</t>
+          <t>-15,46; 57,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,9; 53,5</t>
+          <t>6,01; 53,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-45,14; -13,06</t>
+          <t>-43,2; -14,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 48,47</t>
+          <t>-6,63; 45,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 5,21</t>
+          <t>-11,23; 3,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 3,82</t>
+          <t>-11,1; 2,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 7,1</t>
+          <t>-8,7; 5,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 3,25</t>
+          <t>-8,09; 4,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 1,83</t>
+          <t>-8,49; 3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 5,42</t>
+          <t>-5,29; 8,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,47</t>
+          <t>-7,62; 2,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 1,24</t>
+          <t>-7,87; 1,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 4,76</t>
+          <t>-4,91; 4,58</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-29,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-35,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-11,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-19,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-30,86%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-29,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-35,88%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-11,43%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-2,1%</t>
+          <t>-0,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 83,21</t>
+          <t>-71,11; 44,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 70,36</t>
+          <t>-72,26; 35,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 121,36</t>
+          <t>-55,01; 70,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 42,37</t>
+          <t>-67,94; 80,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,36; 24,57</t>
+          <t>-69,47; 64,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 71,22</t>
+          <t>-42,56; 128,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 30,73</t>
+          <t>-59,63; 26,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 14,66</t>
+          <t>-60,91; 21,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 59,94</t>
+          <t>-39,05; 59,0</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,54</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-6,39</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,54</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 7,44</t>
+          <t>-8,21; 4,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -1,35</t>
+          <t>-8,87; 3,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 7,02</t>
+          <t>-5,84; 9,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 4,67</t>
+          <t>-6,14; 7,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 3,45</t>
+          <t>-12,22; -1,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 10,47</t>
+          <t>-7,38; 6,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,32</t>
+          <t>-5,87; 4,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; -0,3</t>
+          <t>-8,97; -0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,39</t>
+          <t>-4,22; 6,3</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-15,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-25,12%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-72,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,75%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-25,12%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>-0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 151,62</t>
+          <t>-62,5; 75,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,3; 1,66</t>
+          <t>-65,1; 67,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 147,12</t>
+          <t>-45,2; 146,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 78,73</t>
+          <t>-51,01; 147,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 69,42</t>
+          <t>-93,95; -9,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,48; 149,27</t>
+          <t>-60,07; 126,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 60,38</t>
+          <t>-47,92; 63,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 0,57</t>
+          <t>-71,49; -5,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 98,32</t>
+          <t>-37,42; 83,64</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,14</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,35</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-2,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 10,33</t>
+          <t>-8,64; 8,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 6,8</t>
+          <t>-13,53; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 6,42</t>
+          <t>-10,84; 7,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 8,52</t>
+          <t>-3,23; 10,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 0,76</t>
+          <t>-6,64; 5,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 8,43</t>
+          <t>-7,82; 5,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 6,96</t>
+          <t>-4,68; 6,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 1,66</t>
+          <t>-9,03; 1,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,25</t>
+          <t>-7,75; 4,15</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-45,46%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-15,32%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>66,57%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-5,76%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-12,67%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-45,46%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,88%</t>
+          <t>-20,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,66%</t>
+          <t>-21,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 428,17</t>
+          <t>-49,01; 84,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 322,01</t>
+          <t>-75,61; 13,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 351,34</t>
+          <t>-62,44; 82,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 91,63</t>
+          <t>-40,73; 389,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 12,35</t>
+          <t>-81,04; 237,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,05; 90,9</t>
+          <t>-86,77; 263,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 87,29</t>
+          <t>-36,36; 85,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,41; 26,91</t>
+          <t>-67,13; 22,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 72,74</t>
+          <t>-58,83; 55,59</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,89</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,07</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 13,31</t>
+          <t>1,91; 12,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,31</t>
+          <t>-9,05; -0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 11,77</t>
+          <t>-1,78; 9,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,85</t>
+          <t>2,86; 13,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; -0,38</t>
+          <t>-6,02; 2,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 10,26</t>
+          <t>-1,92; 7,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,52</t>
+          <t>3,95; 11,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,1</t>
+          <t>-5,52; 0,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,29</t>
+          <t>-0,33; 7,76</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>72,59%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-47,15%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39,22%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>93,44%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-12,31%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>72,59%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-47,15%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,38; 199,43</t>
+          <t>10,1; 162,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 50,64</t>
+          <t>-73,26; -6,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 179,15</t>
+          <t>-15,54; 124,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,31; 171,47</t>
+          <t>23,24; 208,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,92; -3,09</t>
+          <t>-51,43; 48,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 128,71</t>
+          <t>-20,32; 115,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,94; 151,04</t>
+          <t>35,78; 154,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 2,13</t>
+          <t>-50,96; 6,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 104,34</t>
+          <t>-2,63; 101,56</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,03</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-5,75</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,24</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,69</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,03</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-5,75</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>2,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 8,76</t>
+          <t>-3,46; 10,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 7,86</t>
+          <t>-11,52; 0,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,58</t>
+          <t>-5,43; 20,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 11,13</t>
+          <t>-2,86; 9,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -0,18</t>
+          <t>-3,72; 7,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 23,38</t>
+          <t>-4,25; 8,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 8,44</t>
+          <t>-1,18; 8,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 2,01</t>
+          <t>-6,41; 1,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 15,73</t>
+          <t>-2,23; 13,08</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-45,27%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>38,56%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>20,13%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-45,27%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 175,49</t>
+          <t>-21,74; 114,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 158,13</t>
+          <t>-73,53; 5,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 172,88</t>
+          <t>-38,73; 225,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 119,67</t>
+          <t>-26,6; 186,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 0,67</t>
+          <t>-35,95; 168,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 234,88</t>
+          <t>-39,87; 167,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 102,52</t>
+          <t>-10,1; 94,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 25,87</t>
+          <t>-49,42; 21,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 174,99</t>
+          <t>-21,29; 142,6</t>
         </is>
       </c>
     </row>
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,78</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,08</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-2,27</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>-1,14</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-1,75</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 10,98</t>
+          <t>-10,47; 5,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 4,31</t>
+          <t>-9,48; 8,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 5,62</t>
+          <t>-11,46; 5,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 6,42</t>
+          <t>-5,77; 10,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,35</t>
+          <t>-8,77; 4,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 4,42</t>
+          <t>-7,59; 6,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 6,01</t>
+          <t>-5,37; 6,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 3,75</t>
+          <t>-6,42; 5,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 3,16</t>
+          <t>-7,06; 3,85</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-13,53%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-3,69%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-25,4%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>29,44%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-32,13%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-16,09%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-13,53%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-3,69%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-28,44%</t>
+          <t>-10,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-23,08%</t>
+          <t>-19,52%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 322,21</t>
+          <t>-66,43; 90,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 132,08</t>
+          <t>-64,38; 113,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-77,71; 162,67</t>
+          <t>-71,39; 92,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 91,73</t>
+          <t>-62,25; 255,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,18; 130,1</t>
+          <t>-87,01; 145,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,16; 71,43</t>
+          <t>-73,83; 205,96</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 95,11</t>
+          <t>-46,01; 107,13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 66,38</t>
+          <t>-56,59; 90,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 58,05</t>
+          <t>-61,05; 69,34</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,57</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,38</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,18</t>
+          <t>-0,93; 5,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,85</t>
+          <t>-6,89; -2,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,91</t>
+          <t>-1,74; 5,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,06</t>
+          <t>1,07; 6,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -1,91</t>
+          <t>-3,89; 0,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,14</t>
+          <t>-1,55; 3,86</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,81</t>
+          <t>0,84; 4,77</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,74; -1,3</t>
+          <t>-4,69; -1,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,37</t>
+          <t>-0,97; 3,66</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-38,32%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>43,22%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-18,95%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-38,32%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,03; 87,74</t>
+          <t>-7,69; 53,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 12,14</t>
+          <t>-54,41; -20,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 65,57</t>
+          <t>-14,23; 52,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 52,29</t>
+          <t>11,03; 89,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,25; -18,62</t>
+          <t>-41,41; 10,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 57,83</t>
+          <t>-16,42; 54,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,01; 53,85</t>
+          <t>7,92; 54,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,2; -14,44</t>
+          <t>-44,17; -15,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 45,84</t>
+          <t>-9,17; 40,24</t>
         </is>
       </c>
     </row>
